--- a/bon_commande_RS.xlsx
+++ b/bon_commande_RS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gokay\OneDrive\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antotauv\Documents\Projet_1A_2026\ENSEA_S6_PROJET_OSCILLO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BF970B9-17D6-409F-A934-02E5A2FB686B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE25800-15BF-4253-91CE-D7D8DD5C1036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{77D87443-5627-4F1F-A5BB-202DAC2F1540}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{77D87443-5627-4F1F-A5BB-202DAC2F1540}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>RS France</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>TA.01</t>
-  </si>
-  <si>
-    <t>60</t>
   </si>
   <si>
     <t>18.03.2026</t>
@@ -517,66 +514,66 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76DAC2B1-1F38-4CC7-90D2-72673EDF760E}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="3" spans="1:14" ht="42" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
+    <row r="3" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>10</v>
@@ -585,7 +582,7 @@
         <v>2</v>
       </c>
       <c r="I3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>0.27700000000000002</v>

--- a/bon_commande_RS.xlsx
+++ b/bon_commande_RS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antotauv\Documents\Projet_1A_2026\ENSEA_S6_PROJET_OSCILLO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gokay\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE25800-15BF-4253-91CE-D7D8DD5C1036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{700C59F8-FD50-4923-8DE8-6C7225F6860E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{77D87443-5627-4F1F-A5BB-202DAC2F1540}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{77D87443-5627-4F1F-A5BB-202DAC2F1540}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -514,14 +514,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76DAC2B1-1F38-4CC7-90D2-72673EDF760E}">
   <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -565,7 +565,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>10</v>
       </c>
